--- a/backend/LPG testing/capex-fuels-CleanStep.xlsx
+++ b/backend/LPG testing/capex-fuels-CleanStep.xlsx
@@ -2106,37 +2106,37 @@
         <v>0.08811785021904292</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0.2552864205983739</v>
+        <v>0.2489922884398709</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.3263713228963656</v>
+        <v>0.4025485609454563</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.3111040561758646</v>
+        <v>0.4601572883484399</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.2959894621225687</v>
+        <v>0.4315486084818809</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.2810260140098059</v>
+        <v>0.4032260154139877</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.2286429271891372</v>
+        <v>0.3376173750877399</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.1394027163923602</v>
+        <v>0.2379673858339422</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.09130770040608688</v>
+        <v>0.1419839646758477</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>0.08374465762715648</v>
+        <v>0.08721317043186992</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.07625724527601543</v>
+        <v>0.0730411071778122</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>0.06366102272075755</v>
+        <v>0.05382708022866686</v>
       </c>
     </row>
   </sheetData>
